--- a/backend/data/uploads/MES/2026-07-09_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-09_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A664AAC8-F7F2-4FD8-9437-1717CA0B36E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DED9C5F5-0047-4892-B1AD-AD72E6C02164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{08CF06D9-CA6D-42EB-BE2A-111B16D99CDA}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{778790D1-0B5F-4712-A44A-D5CBF1AC0F1D}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5DB6839-B0EC-41E9-9329-7CFD4844D97F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BBCDC5B-3312-4930-B4F6-E08C9C026457}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-09_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-09_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DED9C5F5-0047-4892-B1AD-AD72E6C02164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2793391-0383-45DD-9C9A-F5E9E23D473E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{778790D1-0B5F-4712-A44A-D5CBF1AC0F1D}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{85EEF5E5-7E7A-40DD-9302-A1A29DB23E85}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BBCDC5B-3312-4930-B4F6-E08C9C026457}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A3469ED-CDBD-4F04-9409-639D14DFF105}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-09_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-09_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2793391-0383-45DD-9C9A-F5E9E23D473E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{512145BC-FDFF-45FC-A0D8-F2C72902396B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{85EEF5E5-7E7A-40DD-9302-A1A29DB23E85}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{46190826-5851-4813-83EB-BC04D993B681}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A3469ED-CDBD-4F04-9409-639D14DFF105}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8658999-9254-41F8-A50D-F791D6DFC79D}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
